--- a/datasets/location_data/phenocam_ald_gps_coordinates.xlsx
+++ b/datasets/location_data/phenocam_ald_gps_coordinates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2277781_ed_ac_uk/Documents/Dissertation/Data/location_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2277781_ed_ac_uk/Documents/Dissertation/Data/location_data/GPS_coordinates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{719C714F-FA37-450A-8E75-447D975C1C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{719C714F-FA37-450A-8E75-447D975C1C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D60DFE-C1F8-48F7-B344-9041BDE110DC}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{F495D1A8-2BD1-4A2D-A7C3-9C14A39990C2}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{F495D1A8-2BD1-4A2D-A7C3-9C14A39990C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
   <si>
     <t>type</t>
   </si>
@@ -84,21 +84,9 @@
     <t>QHI12</t>
   </si>
   <si>
-    <t>lat</t>
-  </si>
-  <si>
-    <t>lon</t>
-  </si>
-  <si>
     <t>Phenocam gps coordinates taken from Isla's folder-&gt; QHI_GPS_Data_2025-&gt; QHI_Phenocams_2025</t>
   </si>
   <si>
-    <t>tomst</t>
-  </si>
-  <si>
-    <t>TOMST gps coordinates taken from same file path as above -&gt; QHI_TOMST_2025</t>
-  </si>
-  <si>
     <t>QHI-PHENOLOGY_DRYINT_02_NEW</t>
   </si>
   <si>
@@ -151,13 +139,49 @@
   </si>
   <si>
     <t xml:space="preserve">then can compare to elevation/satilites to see if these location where lots of slumping/mass movement/on a slope that could help us explain why active layer changes the way it does - and then (eventually) how this could impact the roots </t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>QHI_ITEXPLOTS_KOM_05</t>
+  </si>
+  <si>
+    <t>QHI_ITEXPLOTS_KOM_06</t>
+  </si>
+  <si>
+    <t>QHI_PHENOLOGY_ERIVAG_03</t>
+  </si>
+  <si>
+    <t>QHI_PHENOLOGY_SALARC_01_ALD</t>
+  </si>
+  <si>
+    <t>HE</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>Phenology ridge salix transect NEW</t>
+  </si>
+  <si>
+    <t>Phenology ridge dryas transect NEW</t>
+  </si>
+  <si>
+    <t>Phenology ridge tussock transect</t>
+  </si>
+  <si>
+    <t>Phenology ridge salix transect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +194,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="4"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -192,8 +222,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,10 +559,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FAFA80E-867E-4380-864F-734B6ADCCD15}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,13 +570,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -559,7 +590,7 @@
         <v>-138.90445</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -573,7 +604,7 @@
         <v>-138.90527</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -587,7 +618,7 @@
         <v>-138.91274999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -601,7 +632,7 @@
         <v>-138.89494999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -615,7 +646,7 @@
         <v>-138.86704</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -629,7 +660,7 @@
         <v>-138.86309</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -643,7 +674,7 @@
         <v>-138.88907</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -657,7 +688,7 @@
         <v>-138.89090999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -671,7 +702,7 @@
         <v>-138.90275099999999</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -685,7 +716,7 @@
         <v>-138.90098</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -699,7 +730,7 @@
         <v>-138.89401000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -713,340 +744,276 @@
         <v>-138.86964</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D14">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D15">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16">
+        <v>69.574881039999994</v>
+      </c>
+      <c r="D16">
+        <v>-138.86307059999999</v>
+      </c>
+      <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <v>69.574888920000006</v>
+      </c>
+      <c r="D17">
+        <v>-138.8631728</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18">
+        <v>69.574882380000005</v>
+      </c>
+      <c r="D18">
+        <v>-138.8634658</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19">
+        <v>69.574860330000007</v>
+      </c>
+      <c r="D19">
+        <v>-138.8637913</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>69.574861170000005</v>
+      </c>
+      <c r="D20">
+        <v>-138.86387010000001</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21">
+        <v>69.574857399999999</v>
+      </c>
+      <c r="D21">
+        <v>-138.8640747</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22">
+        <v>69.576416179999995</v>
+      </c>
+      <c r="D22">
+        <v>-138.86817970000001</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23">
+        <v>69.576403529999993</v>
+      </c>
+      <c r="D23">
+        <v>-138.86811879999999</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24">
+        <v>69.576461190000003</v>
+      </c>
+      <c r="D24">
+        <v>-138.86773909999999</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>69.576468489999996</v>
+      </c>
+      <c r="D25">
+        <v>-138.8676384</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26">
+        <v>69.576505789999999</v>
+      </c>
+      <c r="D26">
+        <v>-138.86729539999999</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27">
+        <v>69.576544850000005</v>
+      </c>
+      <c r="D27">
+        <v>-138.86699780000001</v>
+      </c>
+      <c r="E27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D28">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29">
         <v>69.575540020000005</v>
       </c>
-      <c r="D14">
+      <c r="D29">
         <v>-138.90445</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15">
-        <v>69.575689980000007</v>
-      </c>
-      <c r="D15">
-        <v>-138.90527</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16">
-        <v>69.577619990000002</v>
-      </c>
-      <c r="D16">
-        <v>-138.91274999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17">
-        <v>69.574938029999998</v>
-      </c>
-      <c r="D17">
-        <v>-138.89500799999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>69.576507969999994</v>
-      </c>
-      <c r="D18">
-        <v>-138.86704900000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19">
-        <v>69.574826970000004</v>
-      </c>
-      <c r="D19">
-        <v>-138.86308500000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20">
-        <v>69.576073030000003</v>
-      </c>
-      <c r="D20">
-        <v>-138.88910799999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21">
-        <v>69.57706503</v>
-      </c>
-      <c r="D21">
-        <v>-138.89089000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22">
-        <v>69.569847030000005</v>
-      </c>
-      <c r="D22">
-        <v>-138.90281100000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23">
-        <v>69.575949980000004</v>
-      </c>
-      <c r="D23">
-        <v>-138.900972</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24">
-        <v>69.569278990000001</v>
-      </c>
-      <c r="D24">
-        <v>-138.91663800000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25">
-        <v>69.581631990000005</v>
-      </c>
-      <c r="D25">
-        <v>-138.86962600000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26">
-        <v>69.576106809999999</v>
-      </c>
-      <c r="D26">
-        <v>-138.90396720000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27">
-        <v>69.575888039999995</v>
-      </c>
-      <c r="D27">
-        <v>-138.90355299999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28">
-        <v>69.574881039999994</v>
-      </c>
-      <c r="D28">
-        <v>-138.86307059999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29">
-        <v>69.574888920000006</v>
-      </c>
-      <c r="D29">
-        <v>-138.8631728</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30">
-        <v>69.574882380000005</v>
-      </c>
-      <c r="D30">
-        <v>-138.8634658</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31">
-        <v>69.574860330000007</v>
-      </c>
-      <c r="D31">
-        <v>-138.8637913</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32">
-        <v>69.574861170000005</v>
-      </c>
-      <c r="D32">
-        <v>-138.86387010000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33">
-        <v>69.574857399999999</v>
-      </c>
-      <c r="D33">
-        <v>-138.8640747</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34">
-        <v>69.576416179999995</v>
-      </c>
-      <c r="D34">
-        <v>-138.86817970000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35">
-        <v>69.576403529999993</v>
-      </c>
-      <c r="D35">
-        <v>-138.86811879999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36">
-        <v>69.576461190000003</v>
-      </c>
-      <c r="D36">
-        <v>-138.86773909999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37">
-        <v>69.576468489999996</v>
-      </c>
-      <c r="D37">
-        <v>-138.8676384</v>
+      <c r="E29" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1062,97 +1029,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
